--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/bio-bio.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2467,6 +2467,67 @@
         <v>15079.44</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3606-145-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.967.400-6</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>4878.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/bio-bio.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4455-877-CM25</t>
+          <t>1057404-1656-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.602.209-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2326.09</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2760-88-CM25</t>
+          <t>4020-434-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11803.61</v>
+        <v>32587.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2418-90-CM25</t>
+          <t>4493-267-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29988</v>
+        <v>3107.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057931-153-CM25</t>
+          <t>4238-98-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INFO WORLD SA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.532.020-2</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>768.23</v>
+        <v>17754.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4455-1025-CM25</t>
+          <t>1084156-2981-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1903.17</v>
+        <v>26846.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057931-159-CM25</t>
+          <t>1084156-2971-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2749.02</v>
+        <v>4836.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2665-1239-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>211.43</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2410-2648-CM25</t>
+          <t>4455-877-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,32 +981,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>151725</v>
+        <v>2326.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4858-12-CM26</t>
+          <t>2760-88-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19982.48</v>
+        <v>11803.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3019-26-CM26</t>
+          <t>2418-90-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.259.900-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5322.16</v>
+        <v>29988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4455-16-CM26</t>
+          <t>1057931-153-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>INFO WORLD SA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.532.020-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2113.8</v>
+        <v>768.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>483-50-CM26</t>
+          <t>4455-1025-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.103-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5097.96</v>
+        <v>1903.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3019-63-CM26</t>
+          <t>1057931-159-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.259.900-4</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>887.03</v>
+        <v>2749.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3947-89-CM26</t>
+          <t>2665-1239-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.151.400-5</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
+          <t>Dirección de Educación Municipal</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8746.5</v>
+        <v>211.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1208910-21-CM26</t>
+          <t>2410-2648-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.201.852-1</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,28 +1408,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1538.91</v>
+        <v>151725</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4020-202-CM26</t>
+          <t>4858-12-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32562.33</v>
+        <v>19982.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1456840-17-CM26</t>
+          <t>3019-26-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.259.900-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1173.34</v>
+        <v>5322.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4493-122-CM26</t>
+          <t>4455-16-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4169.02</v>
+        <v>2113.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057404-402-CM26</t>
+          <t>483-50-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.209-1</t>
+          <t>61.607.103-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2998.8</v>
+        <v>5097.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>3947-89-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1687,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.151.400-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>72770.88</v>
+        <v>8746.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4454-332-CM26</t>
+          <t>3019-63-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>69.259.900-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2307.83</v>
+        <v>887.03</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4856-134-CM26</t>
+          <t>1208910-21-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>65.201.852-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL DE LA REGIÓN DEL BIOBÍO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2548.98</v>
+        <v>1538.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4238-132-CM26</t>
+          <t>4020-202-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>19514.57</v>
+        <v>32562.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4079-211-CM26</t>
+          <t>1456840-17-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7819.73</v>
+        <v>1173.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057544-9434-CM26</t>
+          <t>4493-122-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1992,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>Ilustre Municipalidad de Penco - Salud</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1203.6</v>
+        <v>4169.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1084156-411-CM26</t>
+          <t>1057404-402-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.602.209-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>9346.26</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4083-257-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5247.9</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3796-350-CM26</t>
+          <t>4454-332-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>35078.96</v>
+        <v>2307.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2360-474-CM26</t>
+          <t>4856-134-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7607.1</v>
+        <v>2548.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2421-857-CM26</t>
+          <t>4238-132-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,27 +2297,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36235.5</v>
+        <v>19514.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2098-1687-CM26</t>
+          <t>4079-211-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.211-3</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>74302.77</v>
+        <v>7819.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4189-468-CM26</t>
+          <t>1057544-9434-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15079.44</v>
+        <v>1203.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3606-145-CM26</t>
+          <t>1084156-411-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,27 +2480,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.967.400-6</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2525,6 +2525,433 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
+        <v>9346.26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4083-257-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.151.002-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>5247.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3796-350-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.172.600-2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>35078.96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2360-474-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.150.800-5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>7607.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2421-857-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.256.900-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dirección de Administración de Salud Municipal</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>36235.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2098-1687-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.602.211-3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>74302.77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4189-468-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.160.300-8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LEBU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>15079.44</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3606-145-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.967.400-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>4878.64</v>
       </c>
     </row>
